--- a/data/quotations.xlsx
+++ b/data/quotations.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AB2"/>
+  <dimension ref="A1:AB3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -571,9 +571,95 @@
         <v>2026-05-31T15:32:14.423Z</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>ee86473c-b3ba-44fc-9656-9f4bd7e43d1d</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>100</v>
+      </c>
+      <c r="E3">
+        <v>16</v>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3">
+        <v>0.42</v>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3">
+        <v>7.1</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>20</v>
+      </c>
+      <c r="M3">
+        <v>3</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>30</v>
+      </c>
+      <c r="P3">
+        <v>12</v>
+      </c>
+      <c r="Q3">
+        <v>800</v>
+      </c>
+      <c r="R3" t="str">
+        <v>draft</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>109.7844</v>
+      </c>
+      <c r="V3">
+        <v>225.1542</v>
+      </c>
+      <c r="W3">
+        <v>247.6696</v>
+      </c>
+      <c r="X3">
+        <v>22.5154</v>
+      </c>
+      <c r="Y3">
+        <v>9.0909</v>
+      </c>
+      <c r="Z3" t="str">
+        <v>QTN-20260531-002</v>
+      </c>
+      <c r="AA3" t="str">
+        <v>2026-05-31T17:01:07.379Z</v>
+      </c>
+      <c r="AB3" t="str">
+        <v>2026-05-31T17:01:07.379Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AB2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AB3"/>
   </ignoredErrors>
 </worksheet>
 </file>